--- a/artfynd/A 58693-2025 artfynd.xlsx
+++ b/artfynd/A 58693-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>79608671</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612757.0823362881</v>
+        <v>612757</v>
       </c>
       <c r="R2" t="n">
-        <v>7185832.059347824</v>
+        <v>7185832</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79608702</v>
+        <v>79608701</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612695.1167132898</v>
+        <v>612814</v>
       </c>
       <c r="R3" t="n">
-        <v>7185922.816117234</v>
+        <v>7185820</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +845,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79608701</v>
+        <v>79608702</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612813.9598186499</v>
+        <v>612695</v>
       </c>
       <c r="R4" t="n">
-        <v>7185820.101122291</v>
+        <v>7185923</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,19 +947,9 @@
           <t>2019-08-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
